--- a/data/processed/companies.xlsx
+++ b/data/processed/companies.xlsx
@@ -1079,7 +1079,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BAJAJAUTO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
